--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_08.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_08.xlsx
@@ -480,25 +480,25 @@
         <v>45870</v>
       </c>
       <c r="B5" t="n">
-        <v>1524.84</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1110.39</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>306.85</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2058</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>398499</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>65936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45871</v>
       </c>
       <c r="B6" t="n">
-        <v>1459.53</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1057.79</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>281.89</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2291</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>391830</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>67328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45872</v>
       </c>
       <c r="B7" t="n">
-        <v>1479.16</v>
+        <v>1513.37</v>
       </c>
       <c r="C7" t="n">
-        <v>23.37</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>1067.36</v>
+        <v>1089.81</v>
       </c>
       <c r="E7" t="n">
-        <v>300.85</v>
+        <v>292.2</v>
       </c>
       <c r="F7" t="n">
-        <v>2231</v>
+        <v>1336</v>
       </c>
       <c r="G7" t="n">
-        <v>392931</v>
+        <v>389833</v>
       </c>
       <c r="H7" t="n">
-        <v>67695</v>
+        <v>66460</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45873</v>
       </c>
       <c r="B8" t="n">
-        <v>1608</v>
+        <v>1349.15</v>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>23.86</v>
       </c>
       <c r="D8" t="n">
-        <v>1170.39</v>
+        <v>975.75</v>
       </c>
       <c r="E8" t="n">
-        <v>318.11</v>
+        <v>276.49</v>
       </c>
       <c r="F8" t="n">
-        <v>2446</v>
+        <v>1243</v>
       </c>
       <c r="G8" t="n">
-        <v>444098</v>
+        <v>357852</v>
       </c>
       <c r="H8" t="n">
-        <v>72100</v>
+        <v>64526</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45874</v>
       </c>
       <c r="B9" t="n">
-        <v>463.26</v>
+        <v>537.76</v>
       </c>
       <c r="C9" t="n">
-        <v>7.86</v>
+        <v>8.24</v>
       </c>
       <c r="D9" t="n">
-        <v>340.54</v>
+        <v>389.81</v>
       </c>
       <c r="E9" t="n">
-        <v>89.67</v>
+        <v>105.08</v>
       </c>
       <c r="F9" t="n">
-        <v>945</v>
+        <v>660</v>
       </c>
       <c r="G9" t="n">
-        <v>133171</v>
+        <v>151591</v>
       </c>
       <c r="H9" t="n">
-        <v>21904</v>
+        <v>23129</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45875</v>
       </c>
       <c r="B10" t="n">
-        <v>1509.01</v>
+        <v>1601.3</v>
       </c>
       <c r="C10" t="n">
-        <v>23.73</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>1086.51</v>
+        <v>1152.7</v>
       </c>
       <c r="E10" t="n">
-        <v>293.38</v>
+        <v>308.03</v>
       </c>
       <c r="F10" t="n">
-        <v>2465</v>
+        <v>1242</v>
       </c>
       <c r="G10" t="n">
-        <v>390798</v>
+        <v>442593</v>
       </c>
       <c r="H10" t="n">
-        <v>70112</v>
+        <v>67187</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45876</v>
       </c>
       <c r="B11" t="n">
-        <v>1519.71</v>
+        <v>1031.89</v>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>1106.38</v>
+        <v>744.01</v>
       </c>
       <c r="E11" t="n">
-        <v>296.89</v>
+        <v>209</v>
       </c>
       <c r="F11" t="n">
-        <v>2253</v>
+        <v>1334</v>
       </c>
       <c r="G11" t="n">
-        <v>394327</v>
+        <v>287232</v>
       </c>
       <c r="H11" t="n">
-        <v>68237</v>
+        <v>47190</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45877</v>
       </c>
       <c r="B12" t="n">
-        <v>1477.67</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1065.67</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>292.83</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2391</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>405857</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>71381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45878</v>
       </c>
       <c r="B13" t="n">
-        <v>1370.24</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>23.06</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>994.4400000000001</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>265.05</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2245</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>350914</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>61212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45879</v>
       </c>
       <c r="B14" t="n">
-        <v>609.05</v>
+        <v>1537.71</v>
       </c>
       <c r="C14" t="n">
-        <v>9.75</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>440.08</v>
+        <v>1120.01</v>
       </c>
       <c r="E14" t="n">
-        <v>122.26</v>
+        <v>316.4</v>
       </c>
       <c r="F14" t="n">
-        <v>1097</v>
+        <v>1437</v>
       </c>
       <c r="G14" t="n">
-        <v>168527</v>
+        <v>403909</v>
       </c>
       <c r="H14" t="n">
-        <v>27545</v>
+        <v>72253</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45880</v>
       </c>
       <c r="B15" t="n">
-        <v>958.91</v>
+        <v>1522.94</v>
       </c>
       <c r="C15" t="n">
-        <v>15.77</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>691.87</v>
+        <v>1109.76</v>
       </c>
       <c r="E15" t="n">
-        <v>186.3</v>
+        <v>304.48</v>
       </c>
       <c r="F15" t="n">
-        <v>1503</v>
+        <v>1341</v>
       </c>
       <c r="G15" t="n">
-        <v>265065</v>
+        <v>370103</v>
       </c>
       <c r="H15" t="n">
-        <v>44201</v>
+        <v>67749</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45881</v>
       </c>
       <c r="B16" t="n">
-        <v>782.9400000000001</v>
+        <v>1536.18</v>
       </c>
       <c r="C16" t="n">
-        <v>13.36</v>
+        <v>23.42</v>
       </c>
       <c r="D16" t="n">
-        <v>563</v>
+        <v>1101.81</v>
       </c>
       <c r="E16" t="n">
-        <v>157.57</v>
+        <v>306.43</v>
       </c>
       <c r="F16" t="n">
-        <v>1780</v>
+        <v>1216</v>
       </c>
       <c r="G16" t="n">
-        <v>219022</v>
+        <v>420252</v>
       </c>
       <c r="H16" t="n">
-        <v>36838</v>
+        <v>69929</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45882</v>
       </c>
       <c r="B17" t="n">
-        <v>652.08</v>
+        <v>1391.49</v>
       </c>
       <c r="C17" t="n">
-        <v>10.4</v>
+        <v>22.87</v>
       </c>
       <c r="D17" t="n">
-        <v>472.79</v>
+        <v>1004.45</v>
       </c>
       <c r="E17" t="n">
-        <v>130.35</v>
+        <v>278.55</v>
       </c>
       <c r="F17" t="n">
-        <v>1229</v>
+        <v>1213</v>
       </c>
       <c r="G17" t="n">
-        <v>195821</v>
+        <v>388206</v>
       </c>
       <c r="H17" t="n">
-        <v>29286</v>
+        <v>60964</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45883</v>
       </c>
       <c r="B18" t="n">
-        <v>1095.93</v>
+        <v>1566.51</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>798.53</v>
+        <v>1130.96</v>
       </c>
       <c r="E18" t="n">
-        <v>214.23</v>
+        <v>314.07</v>
       </c>
       <c r="F18" t="n">
-        <v>2065</v>
+        <v>1169</v>
       </c>
       <c r="G18" t="n">
-        <v>298697</v>
+        <v>410006</v>
       </c>
       <c r="H18" t="n">
-        <v>49455</v>
+        <v>69879</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45884</v>
       </c>
       <c r="B19" t="n">
-        <v>892.95</v>
+        <v>1554.77</v>
       </c>
       <c r="C19" t="n">
-        <v>14.19</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>644.01</v>
+        <v>1122.56</v>
       </c>
       <c r="E19" t="n">
-        <v>179.89</v>
+        <v>310.82</v>
       </c>
       <c r="F19" t="n">
-        <v>1797</v>
+        <v>1502</v>
       </c>
       <c r="G19" t="n">
-        <v>264905</v>
+        <v>418341</v>
       </c>
       <c r="H19" t="n">
-        <v>39026</v>
+        <v>70101</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45885</v>
       </c>
       <c r="B20" t="n">
-        <v>1434.72</v>
+        <v>1454.09</v>
       </c>
       <c r="C20" t="n">
-        <v>22.24</v>
+        <v>23.69</v>
       </c>
       <c r="D20" t="n">
-        <v>1041.35</v>
+        <v>1054.97</v>
       </c>
       <c r="E20" t="n">
-        <v>286.18</v>
+        <v>277.6</v>
       </c>
       <c r="F20" t="n">
-        <v>2193</v>
+        <v>1360</v>
       </c>
       <c r="G20" t="n">
-        <v>402642</v>
+        <v>393641</v>
       </c>
       <c r="H20" t="n">
-        <v>63547</v>
+        <v>65954</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45886</v>
       </c>
       <c r="B21" t="n">
-        <v>1442.62</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1043.69</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>287.13</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>2004</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>374965</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>64408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45887</v>
       </c>
       <c r="B22" t="n">
-        <v>1479.14</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1075.7</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>296.15</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>2415</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>378977</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>66317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45888</v>
       </c>
       <c r="B23" t="n">
-        <v>1443.64</v>
+        <v>1594.72</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>1053.18</v>
+        <v>1152.77</v>
       </c>
       <c r="E23" t="n">
-        <v>282.44</v>
+        <v>314.17</v>
       </c>
       <c r="F23" t="n">
-        <v>2184</v>
+        <v>1710</v>
       </c>
       <c r="G23" t="n">
-        <v>394304</v>
+        <v>426673</v>
       </c>
       <c r="H23" t="n">
-        <v>67170</v>
+        <v>66564</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45889</v>
       </c>
       <c r="B24" t="n">
-        <v>1561.35</v>
+        <v>127.72</v>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>2.08</v>
       </c>
       <c r="D24" t="n">
-        <v>1127.67</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>312.02</v>
+        <v>24.67</v>
       </c>
       <c r="F24" t="n">
-        <v>2320</v>
+        <v>137</v>
       </c>
       <c r="G24" t="n">
-        <v>416225</v>
+        <v>42189</v>
       </c>
       <c r="H24" t="n">
-        <v>70698</v>
+        <v>5865</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45890</v>
       </c>
       <c r="B25" t="n">
-        <v>1418.4</v>
+        <v>1260.68</v>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>19.69</v>
       </c>
       <c r="D25" t="n">
-        <v>1033.17</v>
+        <v>912.6799999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>295.02</v>
+        <v>251.97</v>
       </c>
       <c r="F25" t="n">
-        <v>2011</v>
+        <v>1121</v>
       </c>
       <c r="G25" t="n">
-        <v>405454</v>
+        <v>349716</v>
       </c>
       <c r="H25" t="n">
-        <v>67034</v>
+        <v>54292</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45891</v>
       </c>
       <c r="B26" t="n">
-        <v>1009.24</v>
+        <v>1556.22</v>
       </c>
       <c r="C26" t="n">
-        <v>16.81</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>736.75</v>
+        <v>1132.22</v>
       </c>
       <c r="E26" t="n">
-        <v>196.61</v>
+        <v>310.15</v>
       </c>
       <c r="F26" t="n">
-        <v>1660</v>
+        <v>1596</v>
       </c>
       <c r="G26" t="n">
-        <v>281354</v>
+        <v>391376</v>
       </c>
       <c r="H26" t="n">
-        <v>47337</v>
+        <v>67323</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45892</v>
       </c>
       <c r="B27" t="n">
-        <v>672.67</v>
+        <v>1536.97</v>
       </c>
       <c r="C27" t="n">
-        <v>10.74</v>
+        <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>485.8</v>
+        <v>1125.79</v>
       </c>
       <c r="E27" t="n">
-        <v>136.28</v>
+        <v>318.39</v>
       </c>
       <c r="F27" t="n">
-        <v>1688</v>
+        <v>1627</v>
       </c>
       <c r="G27" t="n">
-        <v>194409</v>
+        <v>384519</v>
       </c>
       <c r="H27" t="n">
-        <v>30414</v>
+        <v>69391</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45893</v>
       </c>
       <c r="B28" t="n">
-        <v>1506.52</v>
+        <v>1491.29</v>
       </c>
       <c r="C28" t="n">
-        <v>22.49</v>
+        <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>1096.39</v>
+        <v>1083.57</v>
       </c>
       <c r="E28" t="n">
-        <v>309.53</v>
+        <v>293.08</v>
       </c>
       <c r="F28" t="n">
-        <v>2301</v>
+        <v>1183</v>
       </c>
       <c r="G28" t="n">
-        <v>404225</v>
+        <v>395561</v>
       </c>
       <c r="H28" t="n">
-        <v>69178</v>
+        <v>69152</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45894</v>
       </c>
       <c r="B29" t="n">
-        <v>1351.53</v>
+        <v>1388.45</v>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>23.18</v>
       </c>
       <c r="D29" t="n">
-        <v>987.27</v>
+        <v>1004.42</v>
       </c>
       <c r="E29" t="n">
-        <v>264.86</v>
+        <v>278.11</v>
       </c>
       <c r="F29" t="n">
-        <v>2119</v>
+        <v>1302</v>
       </c>
       <c r="G29" t="n">
-        <v>337096</v>
+        <v>372538</v>
       </c>
       <c r="H29" t="n">
-        <v>63072</v>
+        <v>67066</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45895</v>
       </c>
       <c r="B30" t="n">
-        <v>566.11</v>
+        <v>1313.47</v>
       </c>
       <c r="C30" t="n">
-        <v>9.09</v>
+        <v>22.11</v>
       </c>
       <c r="D30" t="n">
-        <v>412.17</v>
+        <v>941.8</v>
       </c>
       <c r="E30" t="n">
-        <v>114.32</v>
+        <v>265.84</v>
       </c>
       <c r="F30" t="n">
-        <v>1033</v>
+        <v>1093</v>
       </c>
       <c r="G30" t="n">
-        <v>155698</v>
+        <v>345700</v>
       </c>
       <c r="H30" t="n">
-        <v>25648</v>
+        <v>57610</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45896</v>
       </c>
       <c r="B31" t="n">
-        <v>202.27</v>
+        <v>1340.56</v>
       </c>
       <c r="C31" t="n">
-        <v>3.48</v>
+        <v>23.09</v>
       </c>
       <c r="D31" t="n">
-        <v>147.08</v>
+        <v>973.6900000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>39.96</v>
+        <v>259.22</v>
       </c>
       <c r="F31" t="n">
-        <v>381</v>
+        <v>1239</v>
       </c>
       <c r="G31" t="n">
-        <v>62626</v>
+        <v>375539</v>
       </c>
       <c r="H31" t="n">
-        <v>9365</v>
+        <v>65523</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45897</v>
       </c>
       <c r="B32" t="n">
-        <v>758.9299999999999</v>
+        <v>970.87</v>
       </c>
       <c r="C32" t="n">
-        <v>12.27</v>
+        <v>16.03</v>
       </c>
       <c r="D32" t="n">
-        <v>547.8</v>
+        <v>694.62</v>
       </c>
       <c r="E32" t="n">
-        <v>145.96</v>
+        <v>193.22</v>
       </c>
       <c r="F32" t="n">
-        <v>1178</v>
+        <v>1025</v>
       </c>
       <c r="G32" t="n">
-        <v>221808</v>
+        <v>265442</v>
       </c>
       <c r="H32" t="n">
-        <v>34714</v>
+        <v>42659</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45898</v>
       </c>
       <c r="B33" t="n">
-        <v>1025.02</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>17.56</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>744.52</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>201.55</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1707</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>281296</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>45019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45899</v>
       </c>
       <c r="B34" t="n">
-        <v>802.23</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>12.14</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>584.02</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>159.6</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1460</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>202103</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>38673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1260,25 +1260,25 @@
         <v>45900</v>
       </c>
       <c r="B35" t="n">
-        <v>1033.91</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>16.34</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>745.12</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>204.67</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>1946</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>316804</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>49969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1288,25 +1288,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>35111.58000000001</v>
+        <v>29178.11</v>
       </c>
       <c r="C37" t="n">
-        <v>565.23</v>
+        <v>465.26</v>
       </c>
       <c r="D37" t="n">
-        <v>25471.43</v>
+        <v>21110.87</v>
       </c>
       <c r="E37" t="n">
-        <v>6968.4</v>
+        <v>5807.97</v>
       </c>
       <c r="F37" t="n">
-        <v>57396</v>
+        <v>27086</v>
       </c>
       <c r="G37" t="n">
-        <v>9544448</v>
+        <v>7782812</v>
       </c>
       <c r="H37" t="n">
-        <v>1604819</v>
+        <v>1310766</v>
       </c>
     </row>
   </sheetData>

--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_08.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_08.xlsx
@@ -480,25 +480,25 @@
         <v>45870</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1190.76</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>861.12</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>236.76</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1427</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>329166</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>54620</v>
       </c>
     </row>
     <row r="6">
@@ -532,25 +532,25 @@
         <v>45872</v>
       </c>
       <c r="B7" t="n">
-        <v>1513.37</v>
+        <v>1403.4</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>1089.81</v>
+        <v>1014.43</v>
       </c>
       <c r="E7" t="n">
-        <v>292.2</v>
+        <v>280.94</v>
       </c>
       <c r="F7" t="n">
-        <v>1336</v>
+        <v>1157</v>
       </c>
       <c r="G7" t="n">
-        <v>389833</v>
+        <v>379734</v>
       </c>
       <c r="H7" t="n">
-        <v>66460</v>
+        <v>63656</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45873</v>
       </c>
       <c r="B8" t="n">
-        <v>1349.15</v>
+        <v>1435.64</v>
       </c>
       <c r="C8" t="n">
-        <v>23.86</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>975.75</v>
+        <v>1039.41</v>
       </c>
       <c r="E8" t="n">
-        <v>276.49</v>
+        <v>288.72</v>
       </c>
       <c r="F8" t="n">
-        <v>1243</v>
+        <v>1161</v>
       </c>
       <c r="G8" t="n">
-        <v>357852</v>
+        <v>369431</v>
       </c>
       <c r="H8" t="n">
-        <v>64526</v>
+        <v>64979</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45874</v>
       </c>
       <c r="B9" t="n">
-        <v>537.76</v>
+        <v>464.7</v>
       </c>
       <c r="C9" t="n">
-        <v>8.24</v>
+        <v>7.81</v>
       </c>
       <c r="D9" t="n">
-        <v>389.81</v>
+        <v>340.18</v>
       </c>
       <c r="E9" t="n">
-        <v>105.08</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>660</v>
+        <v>603</v>
       </c>
       <c r="G9" t="n">
-        <v>151591</v>
+        <v>132701</v>
       </c>
       <c r="H9" t="n">
-        <v>23129</v>
+        <v>20825</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45875</v>
       </c>
       <c r="B10" t="n">
-        <v>1601.3</v>
+        <v>1543.45</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>23.84</v>
       </c>
       <c r="D10" t="n">
-        <v>1152.7</v>
+        <v>1124.49</v>
       </c>
       <c r="E10" t="n">
-        <v>308.03</v>
+        <v>305.65</v>
       </c>
       <c r="F10" t="n">
-        <v>1242</v>
+        <v>1201</v>
       </c>
       <c r="G10" t="n">
-        <v>442593</v>
+        <v>369028</v>
       </c>
       <c r="H10" t="n">
-        <v>67187</v>
+        <v>70571</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45876</v>
       </c>
       <c r="B11" t="n">
-        <v>1031.89</v>
+        <v>1480.7</v>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>744.01</v>
+        <v>1078.28</v>
       </c>
       <c r="E11" t="n">
-        <v>209</v>
+        <v>295.46</v>
       </c>
       <c r="F11" t="n">
-        <v>1334</v>
+        <v>1354</v>
       </c>
       <c r="G11" t="n">
-        <v>287232</v>
+        <v>382247</v>
       </c>
       <c r="H11" t="n">
-        <v>47190</v>
+        <v>68988</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45877</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>749.5599999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>12.65</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>547.1900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>148.55</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>878</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>208038</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>35447</v>
       </c>
     </row>
     <row r="13">
@@ -714,25 +714,25 @@
         <v>45879</v>
       </c>
       <c r="B14" t="n">
-        <v>1537.71</v>
+        <v>1537.63</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>1120.01</v>
+        <v>1112.86</v>
       </c>
       <c r="E14" t="n">
-        <v>316.4</v>
+        <v>315.16</v>
       </c>
       <c r="F14" t="n">
-        <v>1437</v>
+        <v>1469</v>
       </c>
       <c r="G14" t="n">
-        <v>403909</v>
+        <v>399441</v>
       </c>
       <c r="H14" t="n">
-        <v>72253</v>
+        <v>66771</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45880</v>
       </c>
       <c r="B15" t="n">
-        <v>1522.94</v>
+        <v>1391.96</v>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>22.58</v>
       </c>
       <c r="D15" t="n">
-        <v>1109.76</v>
+        <v>1007.25</v>
       </c>
       <c r="E15" t="n">
-        <v>304.48</v>
+        <v>276.67</v>
       </c>
       <c r="F15" t="n">
-        <v>1341</v>
+        <v>1313</v>
       </c>
       <c r="G15" t="n">
-        <v>370103</v>
+        <v>381983</v>
       </c>
       <c r="H15" t="n">
-        <v>67749</v>
+        <v>62634</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45881</v>
       </c>
       <c r="B16" t="n">
-        <v>1536.18</v>
+        <v>1453.56</v>
       </c>
       <c r="C16" t="n">
-        <v>23.42</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>1101.81</v>
+        <v>1055.66</v>
       </c>
       <c r="E16" t="n">
-        <v>306.43</v>
+        <v>296.12</v>
       </c>
       <c r="F16" t="n">
-        <v>1216</v>
+        <v>1339</v>
       </c>
       <c r="G16" t="n">
-        <v>420252</v>
+        <v>382974</v>
       </c>
       <c r="H16" t="n">
-        <v>69929</v>
+        <v>68222</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45882</v>
       </c>
       <c r="B17" t="n">
-        <v>1391.49</v>
+        <v>1581.45</v>
       </c>
       <c r="C17" t="n">
-        <v>22.87</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>1004.45</v>
+        <v>1145.09</v>
       </c>
       <c r="E17" t="n">
-        <v>278.55</v>
+        <v>317.17</v>
       </c>
       <c r="F17" t="n">
-        <v>1213</v>
+        <v>1381</v>
       </c>
       <c r="G17" t="n">
-        <v>388206</v>
+        <v>432728</v>
       </c>
       <c r="H17" t="n">
-        <v>60964</v>
+        <v>73078</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45883</v>
       </c>
       <c r="B18" t="n">
-        <v>1566.51</v>
+        <v>1390.57</v>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>23.51</v>
       </c>
       <c r="D18" t="n">
-        <v>1130.96</v>
+        <v>1006.79</v>
       </c>
       <c r="E18" t="n">
-        <v>314.07</v>
+        <v>280.15</v>
       </c>
       <c r="F18" t="n">
-        <v>1169</v>
+        <v>1251</v>
       </c>
       <c r="G18" t="n">
-        <v>410006</v>
+        <v>362209</v>
       </c>
       <c r="H18" t="n">
-        <v>69879</v>
+        <v>59553</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45884</v>
       </c>
       <c r="B19" t="n">
-        <v>1554.77</v>
+        <v>1473.53</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>1122.56</v>
+        <v>1069.45</v>
       </c>
       <c r="E19" t="n">
-        <v>310.82</v>
+        <v>287.28</v>
       </c>
       <c r="F19" t="n">
-        <v>1502</v>
+        <v>1365</v>
       </c>
       <c r="G19" t="n">
-        <v>418341</v>
+        <v>391813</v>
       </c>
       <c r="H19" t="n">
-        <v>70101</v>
+        <v>65359</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45885</v>
       </c>
       <c r="B20" t="n">
-        <v>1454.09</v>
+        <v>1487.26</v>
       </c>
       <c r="C20" t="n">
-        <v>23.69</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>1054.97</v>
+        <v>1077.38</v>
       </c>
       <c r="E20" t="n">
-        <v>277.6</v>
+        <v>304.86</v>
       </c>
       <c r="F20" t="n">
-        <v>1360</v>
+        <v>1165</v>
       </c>
       <c r="G20" t="n">
-        <v>393641</v>
+        <v>414615</v>
       </c>
       <c r="H20" t="n">
-        <v>65954</v>
+        <v>64908</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45886</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1286.25</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>20.37</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>932.23</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>253.77</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1214</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>325732</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>58084</v>
       </c>
     </row>
     <row r="22">
@@ -948,25 +948,25 @@
         <v>45888</v>
       </c>
       <c r="B23" t="n">
-        <v>1594.72</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1152.77</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>314.17</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1710</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>426673</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>66564</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45889</v>
       </c>
       <c r="B24" t="n">
-        <v>127.72</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>92.70999999999999</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>24.67</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>42189</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>5865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45890</v>
       </c>
       <c r="B25" t="n">
-        <v>1260.68</v>
+        <v>1533.74</v>
       </c>
       <c r="C25" t="n">
-        <v>19.69</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>912.6799999999999</v>
+        <v>1105.78</v>
       </c>
       <c r="E25" t="n">
-        <v>251.97</v>
+        <v>303.97</v>
       </c>
       <c r="F25" t="n">
-        <v>1121</v>
+        <v>1833</v>
       </c>
       <c r="G25" t="n">
-        <v>349716</v>
+        <v>390049</v>
       </c>
       <c r="H25" t="n">
-        <v>54292</v>
+        <v>69602</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45891</v>
       </c>
       <c r="B26" t="n">
-        <v>1556.22</v>
+        <v>1335.6</v>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>22.01</v>
       </c>
       <c r="D26" t="n">
-        <v>1132.22</v>
+        <v>965.53</v>
       </c>
       <c r="E26" t="n">
-        <v>310.15</v>
+        <v>267.82</v>
       </c>
       <c r="F26" t="n">
-        <v>1596</v>
+        <v>1366</v>
       </c>
       <c r="G26" t="n">
-        <v>391376</v>
+        <v>337618</v>
       </c>
       <c r="H26" t="n">
-        <v>67323</v>
+        <v>62660</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45892</v>
       </c>
       <c r="B27" t="n">
-        <v>1536.97</v>
+        <v>1380.88</v>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>20.67</v>
       </c>
       <c r="D27" t="n">
-        <v>1125.79</v>
+        <v>993.63</v>
       </c>
       <c r="E27" t="n">
-        <v>318.39</v>
+        <v>267.58</v>
       </c>
       <c r="F27" t="n">
-        <v>1627</v>
+        <v>1154</v>
       </c>
       <c r="G27" t="n">
-        <v>384519</v>
+        <v>394671</v>
       </c>
       <c r="H27" t="n">
-        <v>69391</v>
+        <v>63504</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45893</v>
       </c>
       <c r="B28" t="n">
-        <v>1491.29</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>1083.57</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>293.08</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1183</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>395561</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>69152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45894</v>
       </c>
       <c r="B29" t="n">
-        <v>1388.45</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>23.18</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>1004.42</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>278.11</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1302</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>372538</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>67066</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45895</v>
       </c>
       <c r="B30" t="n">
-        <v>1313.47</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>22.11</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>941.8</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>265.84</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1093</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>345700</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>57610</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45896</v>
       </c>
       <c r="B31" t="n">
-        <v>1340.56</v>
+        <v>1441.97</v>
       </c>
       <c r="C31" t="n">
-        <v>23.09</v>
+        <v>23.24</v>
       </c>
       <c r="D31" t="n">
-        <v>973.6900000000001</v>
+        <v>1043.17</v>
       </c>
       <c r="E31" t="n">
-        <v>259.22</v>
+        <v>282.73</v>
       </c>
       <c r="F31" t="n">
-        <v>1239</v>
+        <v>1392</v>
       </c>
       <c r="G31" t="n">
-        <v>375539</v>
+        <v>374603</v>
       </c>
       <c r="H31" t="n">
-        <v>65523</v>
+        <v>65492</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45897</v>
       </c>
       <c r="B32" t="n">
-        <v>970.87</v>
+        <v>1431.56</v>
       </c>
       <c r="C32" t="n">
-        <v>16.03</v>
+        <v>22.76</v>
       </c>
       <c r="D32" t="n">
-        <v>694.62</v>
+        <v>1034.96</v>
       </c>
       <c r="E32" t="n">
-        <v>193.22</v>
+        <v>290.49</v>
       </c>
       <c r="F32" t="n">
-        <v>1025</v>
+        <v>1460</v>
       </c>
       <c r="G32" t="n">
-        <v>265442</v>
+        <v>370590</v>
       </c>
       <c r="H32" t="n">
-        <v>42659</v>
+        <v>65170</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45898</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1440.48</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1038.65</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>289.23</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1498</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>354021</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>70902</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45899</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>1554.29</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>23.98</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1121.13</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>312.38</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1547</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>406599</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>74305</v>
       </c>
     </row>
     <row r="35">
@@ -1288,25 +1288,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29178.11</v>
+        <v>29988.94</v>
       </c>
       <c r="C37" t="n">
-        <v>465.26</v>
+        <v>482.72</v>
       </c>
       <c r="D37" t="n">
-        <v>21110.87</v>
+        <v>21714.66</v>
       </c>
       <c r="E37" t="n">
-        <v>5807.97</v>
+        <v>5992.81</v>
       </c>
       <c r="F37" t="n">
-        <v>27086</v>
+        <v>28528</v>
       </c>
       <c r="G37" t="n">
-        <v>7782812</v>
+        <v>7889991</v>
       </c>
       <c r="H37" t="n">
-        <v>1310766</v>
+        <v>1369330</v>
       </c>
     </row>
   </sheetData>
